--- a/source/xlsx/A2/unit-3/Deutsch_Heimkehr_A2_U3_L4_v1.0.xlsx
+++ b/source/xlsx/A2/unit-3/Deutsch_Heimkehr_A2_U3_L4_v1.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Personal Stuff\Docs\GermanCourseApp\deutsch_heimkehr\source\xlsx\A2\unit-3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E308896-882B-4CE4-8447-B0E7D37F94DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8EA0384-43C4-4AD7-A8BA-D960F4F6A7AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lesson" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="584">
   <si>
     <t>Deutsch Heimkehr</t>
   </si>
@@ -1239,12 +1239,6 @@
     <t>Answer</t>
   </si>
   <si>
-    <t>Skill</t>
-  </si>
-  <si>
-    <t>Difficulty</t>
-  </si>
-  <si>
     <t>A2-U3-L4-Q01</t>
   </si>
   <si>
@@ -1260,12 +1254,6 @@
     <t>Husten means cough.</t>
   </si>
   <si>
-    <t>Vocabulary</t>
-  </si>
-  <si>
-    <t>Easy</t>
-  </si>
-  <si>
     <t>A2-U3-L4-Q02</t>
   </si>
   <si>
@@ -1356,9 +1344,6 @@
     <t>Krankenversicherung means health insurance.</t>
   </si>
   <si>
-    <t>Medium</t>
-  </si>
-  <si>
     <t>A2-U3-L4-Q09</t>
   </si>
   <si>
@@ -1374,9 +1359,6 @@
     <t>The correct first-person form of sich fühlen is ich fühle mich.</t>
   </si>
   <si>
-    <t>Grammar</t>
-  </si>
-  <si>
     <t>A2-U3-L4-Q10</t>
   </si>
   <si>
@@ -1500,9 +1482,6 @@
     <t>This is a formal imperative often used by doctors.</t>
   </si>
   <si>
-    <t>Dialogue</t>
-  </si>
-  <si>
     <t>A2-U3-L4-Q20</t>
   </si>
   <si>
@@ -1527,9 +1506,6 @@
     <t>Sofia calls because she feels sick and needs a doctor's appointment.</t>
   </si>
   <si>
-    <t>Reading</t>
-  </si>
-  <si>
     <t>A2-U3-L4-Q22</t>
   </si>
   <si>
@@ -1674,9 +1650,6 @@
     <t>This is the standard phrase for requesting an appointment.</t>
   </si>
   <si>
-    <t>Functional Language</t>
-  </si>
-  <si>
     <t>A2-U3-L4-Q32</t>
   </si>
   <si>
@@ -1701,9 +1674,6 @@
     <t>An Apotheke is a pharmacy.</t>
   </si>
   <si>
-    <t>Culture</t>
-  </si>
-  <si>
     <t>A2-U3-L4-Q34</t>
   </si>
   <si>
@@ -1780,9 +1750,6 @@
   </si>
   <si>
     <t>Answers may vary; a correct response can use Ich fühle mich... plus an adjective.</t>
-  </si>
-  <si>
-    <t>Writing</t>
   </si>
   <si>
     <t>A2-U3-L4-Q40</t>
@@ -2074,7 +2041,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B40"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
@@ -2096,7 +2063,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="27.6">
+    <row r="3" spans="1:2" ht="28.5">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -2104,7 +2071,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" ht="15">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -2112,7 +2079,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" ht="15">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
@@ -2120,7 +2087,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" ht="15">
       <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
@@ -2128,7 +2095,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" ht="15">
       <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
@@ -2144,7 +2111,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="55.2">
+    <row r="9" spans="1:2" ht="57">
       <c r="A9" s="5" t="s">
         <v>16</v>
       </c>
@@ -2152,7 +2119,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="41.4">
+    <row r="10" spans="1:2" ht="42.75">
       <c r="A10" s="5" t="s">
         <v>18</v>
       </c>
@@ -2160,7 +2127,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="55.2">
+    <row r="11" spans="1:2" ht="57">
       <c r="A11" s="5" t="s">
         <v>20</v>
       </c>
@@ -2168,7 +2135,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="55.2">
+    <row r="12" spans="1:2" ht="57">
       <c r="A12" s="5" t="s">
         <v>22</v>
       </c>
@@ -2176,7 +2143,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="41.4">
+    <row r="13" spans="1:2" ht="42.75">
       <c r="A13" s="5" t="s">
         <v>24</v>
       </c>
@@ -2184,7 +2151,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="55.2">
+    <row r="14" spans="1:2" ht="57">
       <c r="A14" s="5" t="s">
         <v>26</v>
       </c>
@@ -2192,7 +2159,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="41.4">
+    <row r="15" spans="1:2" ht="42.75">
       <c r="A15" s="5" t="s">
         <v>28</v>
       </c>
@@ -2200,7 +2167,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="27.6">
+    <row r="16" spans="1:2" ht="28.5">
       <c r="A16" s="5" t="s">
         <v>30</v>
       </c>
@@ -2208,7 +2175,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="27.6">
+    <row r="17" spans="1:2" ht="28.5">
       <c r="A17" s="5" t="s">
         <v>32</v>
       </c>
@@ -2316,7 +2283,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -2324,7 +2291,7 @@
     <col min="4" max="4" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.05" customHeight="1">
+    <row r="1" spans="1:4" ht="16.149999999999999" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>34</v>
       </c>
@@ -2338,7 +2305,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="28.8" customHeight="1">
+    <row r="2" spans="1:4" ht="28.9" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>38</v>
       </c>
@@ -2352,7 +2319,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="28.8" customHeight="1">
+    <row r="3" spans="1:4" ht="28.9" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>42</v>
       </c>
@@ -2366,7 +2333,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="28.8" customHeight="1">
+    <row r="4" spans="1:4" ht="28.9" customHeight="1">
       <c r="A4" s="5" t="s">
         <v>46</v>
       </c>
@@ -2380,7 +2347,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="28.8" customHeight="1">
+    <row r="5" spans="1:4" ht="28.9" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>50</v>
       </c>
@@ -2394,7 +2361,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="28.8" customHeight="1">
+    <row r="6" spans="1:4" ht="28.9" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>54</v>
       </c>
@@ -2408,7 +2375,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="28.8" customHeight="1">
+    <row r="7" spans="1:4" ht="28.9" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>58</v>
       </c>
@@ -2422,7 +2389,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="28.8" customHeight="1">
+    <row r="8" spans="1:4" ht="28.9" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>62</v>
       </c>
@@ -2436,7 +2403,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="28.8" customHeight="1">
+    <row r="9" spans="1:4" ht="28.9" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>66</v>
       </c>
@@ -2450,7 +2417,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="28.8" customHeight="1">
+    <row r="10" spans="1:4" ht="28.9" customHeight="1">
       <c r="A10" s="5" t="s">
         <v>70</v>
       </c>
@@ -2464,7 +2431,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="28.8" customHeight="1">
+    <row r="11" spans="1:4" ht="28.9" customHeight="1">
       <c r="A11" s="5" t="s">
         <v>74</v>
       </c>
@@ -2478,7 +2445,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="28.8" customHeight="1">
+    <row r="12" spans="1:4" ht="28.9" customHeight="1">
       <c r="A12" s="5" t="s">
         <v>77</v>
       </c>
@@ -2492,7 +2459,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="28.8" customHeight="1">
+    <row r="13" spans="1:4" ht="28.9" customHeight="1">
       <c r="A13" s="5" t="s">
         <v>81</v>
       </c>
@@ -2506,7 +2473,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="28.8" customHeight="1">
+    <row r="14" spans="1:4" ht="28.9" customHeight="1">
       <c r="A14" s="5" t="s">
         <v>85</v>
       </c>
@@ -2520,7 +2487,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="28.8" customHeight="1">
+    <row r="15" spans="1:4" ht="28.9" customHeight="1">
       <c r="A15" s="5" t="s">
         <v>89</v>
       </c>
@@ -2534,7 +2501,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="28.8" customHeight="1">
+    <row r="16" spans="1:4" ht="28.9" customHeight="1">
       <c r="A16" s="5" t="s">
         <v>93</v>
       </c>
@@ -2548,7 +2515,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="28.8" customHeight="1">
+    <row r="17" spans="1:4" ht="28.9" customHeight="1">
       <c r="A17" s="5" t="s">
         <v>97</v>
       </c>
@@ -2562,7 +2529,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="28.8" customHeight="1">
+    <row r="18" spans="1:4" ht="28.9" customHeight="1">
       <c r="A18" s="5" t="s">
         <v>101</v>
       </c>
@@ -2576,7 +2543,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="28.8" customHeight="1">
+    <row r="19" spans="1:4" ht="28.9" customHeight="1">
       <c r="A19" s="5" t="s">
         <v>105</v>
       </c>
@@ -2590,7 +2557,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="28.8" customHeight="1">
+    <row r="20" spans="1:4" ht="28.9" customHeight="1">
       <c r="A20" s="5" t="s">
         <v>109</v>
       </c>
@@ -2604,7 +2571,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="28.8" customHeight="1">
+    <row r="21" spans="1:4" ht="28.9" customHeight="1">
       <c r="A21" s="5" t="s">
         <v>112</v>
       </c>
@@ -2618,7 +2585,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="28.8" customHeight="1">
+    <row r="22" spans="1:4" ht="28.9" customHeight="1">
       <c r="A22" s="5" t="s">
         <v>116</v>
       </c>
@@ -3116,7 +3083,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="3" width="65" customWidth="1"/>
@@ -3133,7 +3100,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="27.6">
+    <row r="2" spans="1:3" ht="30">
       <c r="A2" s="4" t="s">
         <v>249</v>
       </c>
@@ -3144,7 +3111,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="27.6">
+    <row r="3" spans="1:3" ht="30">
       <c r="A3" s="4" t="s">
         <v>252</v>
       </c>
@@ -3155,7 +3122,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="27.6">
+    <row r="4" spans="1:3" ht="28.5">
       <c r="A4" s="4" t="s">
         <v>255</v>
       </c>
@@ -3166,7 +3133,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="27.6">
+    <row r="5" spans="1:3" ht="28.5">
       <c r="A5" s="4" t="s">
         <v>258</v>
       </c>
@@ -3177,7 +3144,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="27.6">
+    <row r="6" spans="1:3" ht="28.5">
       <c r="A6" s="4" t="s">
         <v>261</v>
       </c>
@@ -3188,7 +3155,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="27.6">
+    <row r="7" spans="1:3" ht="28.5">
       <c r="A7" s="4" t="s">
         <v>264</v>
       </c>
@@ -3199,7 +3166,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="27.6">
+    <row r="8" spans="1:3" ht="28.5">
       <c r="A8" s="5" t="s">
         <v>267</v>
       </c>
@@ -3210,7 +3177,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="27.6">
+    <row r="9" spans="1:3" ht="28.5">
       <c r="A9" s="5" t="s">
         <v>270</v>
       </c>
@@ -3221,7 +3188,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="27.6">
+    <row r="10" spans="1:3" ht="30">
       <c r="A10" s="9" t="s">
         <v>273</v>
       </c>
@@ -3232,7 +3199,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" ht="15">
       <c r="A11" s="4" t="s">
         <v>276</v>
       </c>
@@ -3240,10 +3207,10 @@
         <v>277</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15">
       <c r="A12" s="4" t="s">
         <v>276</v>
       </c>
@@ -3251,10 +3218,10 @@
         <v>277</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15">
       <c r="A13" s="4" t="s">
         <v>276</v>
       </c>
@@ -3262,10 +3229,10 @@
         <v>277</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15">
       <c r="A14" s="4" t="s">
         <v>276</v>
       </c>
@@ -3273,7 +3240,7 @@
         <v>277</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>593</v>
+        <v>582</v>
       </c>
     </row>
   </sheetData>
@@ -3284,7 +3251,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C40"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="3" width="65" customWidth="1"/>
@@ -3642,7 +3609,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="27.6">
+    <row r="33" spans="1:3" ht="28.5">
       <c r="A33" s="5" t="s">
         <v>341</v>
       </c>
@@ -3738,7 +3705,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D52"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
     <col min="2" max="2" width="48" customWidth="1"/>
@@ -3754,20 +3721,20 @@
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" ht="15">
       <c r="A2" s="8" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" ht="15">
       <c r="A3" s="8"/>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" ht="15">
       <c r="A4" s="8" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" ht="15">
       <c r="A5" s="8" t="s">
         <v>364</v>
       </c>
@@ -3798,7 +3765,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="27.6">
+    <row r="12" spans="1:4" ht="28.5">
       <c r="A12" s="5" t="s">
         <v>369</v>
       </c>
@@ -3829,7 +3796,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="27.6">
+    <row r="19" spans="1:1" ht="28.5">
       <c r="A19" s="5" t="s">
         <v>374</v>
       </c>
@@ -3855,7 +3822,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="25" spans="1:1" ht="27.6">
+    <row r="25" spans="1:1" ht="28.5">
       <c r="A25" s="5" t="s">
         <v>378</v>
       </c>
@@ -3894,7 +3861,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" ht="28.5">
       <c r="A34" s="5" t="s">
         <v>384</v>
       </c>
@@ -3920,7 +3887,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="40" spans="1:1" ht="27.6">
+    <row r="40" spans="1:1" ht="28.5">
       <c r="A40" s="5" t="s">
         <v>388</v>
       </c>
@@ -3933,7 +3900,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="43" spans="1:1" ht="27.6">
+    <row r="43" spans="1:1" ht="28.5">
       <c r="A43" s="5" t="s">
         <v>390</v>
       </c>
@@ -3946,7 +3913,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="46" spans="1:1" ht="27.6">
+    <row r="46" spans="1:1" ht="28.5">
       <c r="A46" s="5" t="s">
         <v>392</v>
       </c>
@@ -3984,8 +3951,8 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:L42"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <dimension ref="A1:J42"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -3993,12 +3960,10 @@
     <col min="4" max="4" width="50" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
     <col min="6" max="6" width="70" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="12" max="12" width="90" customWidth="1"/>
+    <col min="10" max="10" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="27.6">
+    <row r="1" spans="1:10" ht="30">
       <c r="A1" s="8" t="s">
         <v>397</v>
       </c>
@@ -4009,10 +3974,8 @@
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
       <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-    </row>
-    <row r="2" spans="1:12" ht="45.6" customHeight="1">
+    </row>
+    <row r="2" spans="1:10" ht="45.6" customHeight="1">
       <c r="A2" s="8" t="s">
         <v>399</v>
       </c>
@@ -4031,1037 +3994,791 @@
       <c r="F2" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>404</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>405</v>
-      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-    </row>
-    <row r="3" spans="1:12" ht="12" customHeight="1">
+    </row>
+    <row r="3" spans="1:10" ht="12" customHeight="1">
       <c r="A3" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>407</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>409</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>55</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>410</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>412</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="1:12">
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="5" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>162</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="H4" s="5" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:10">
       <c r="A5" s="5" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>67</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="5" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>182</v>
       </c>
       <c r="F6" s="5" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="C7" s="5" t="s">
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="B8" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>429</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>432</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>433</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>205</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="27.6">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="28.5">
       <c r="A9" s="5" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>177</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="27.6">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="28.5">
       <c r="A10" s="5" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>197</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>442</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="5" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F12" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="G11" s="5" t="s">
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="H11" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="5" t="s">
+      <c r="B13" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>451</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>457</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
         <v>232</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="5" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="27.6">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="28.5">
       <c r="A15" s="5" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>64</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>466</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="5" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="5" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="5" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>223</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="5" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="5" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
         <v>211</v>
       </c>
       <c r="F20" s="5" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="28.5">
+      <c r="A21" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="27.6">
-      <c r="A21" s="5" t="s">
+      <c r="B22" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="C21" s="5" t="s">
+      <c r="D22" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>487</v>
       </c>
-      <c r="D21" s="5" t="s">
+    </row>
+    <row r="23" spans="1:6" ht="28.5">
+      <c r="A23" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="B23" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>489</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="E23" s="5" t="s">
         <v>491</v>
       </c>
-      <c r="H21" s="5" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="5" t="s">
+      <c r="F23" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="C22" s="5" t="s">
+    </row>
+    <row r="24" spans="1:6" ht="42.75">
+      <c r="A24" s="5" t="s">
         <v>493</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="F22" s="5" t="s">
+      <c r="B24" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>494</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="27.6">
-      <c r="A23" s="5" t="s">
+      <c r="D24" s="5" t="s">
         <v>495</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="C23" s="5" t="s">
+      <c r="E24" s="5" t="s">
         <v>496</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="F24" s="5" t="s">
         <v>497</v>
       </c>
-      <c r="E23" s="5" t="s">
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="5" t="s">
         <v>498</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="B25" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>499</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>500</v>
       </c>
-      <c r="H23" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="41.4">
-      <c r="A24" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>501</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="C24" s="5" t="s">
+      <c r="F25" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="D24" s="5" t="s">
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="5" t="s">
         <v>503</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="B26" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>504</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>505</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>500</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="5" t="s">
+      <c r="E26" s="5" t="s">
         <v>506</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="C25" s="5" t="s">
+      <c r="F26" s="5" t="s">
         <v>507</v>
       </c>
-      <c r="D25" s="5" t="s">
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="5" t="s">
         <v>508</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="B27" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>509</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="D27" s="5" t="s">
         <v>510</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>491</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="5" t="s">
+      <c r="E27" s="5" t="s">
         <v>511</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="C26" s="5" t="s">
+      <c r="F27" s="5" t="s">
         <v>512</v>
       </c>
-      <c r="D26" s="5" t="s">
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="B28" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>514</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="D28" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>515</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>500</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="5" t="s">
+      <c r="F28" s="5" t="s">
         <v>516</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="C27" s="5" t="s">
+    </row>
+    <row r="29" spans="1:6" ht="28.5">
+      <c r="A29" s="5" t="s">
         <v>517</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="B29" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>518</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="D29" s="5" t="s">
         <v>519</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="E29" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>500</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="5" t="s">
+      <c r="F29" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="C28" s="5" t="s">
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="E28" s="5" t="s">
+      <c r="B30" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>523</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="D30" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="G28" s="5" t="s">
-        <v>500</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="27.6">
-      <c r="A29" s="5" t="s">
+      <c r="E30" s="5" t="s">
         <v>525</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="C29" s="5" t="s">
+      <c r="F30" s="5" t="s">
         <v>526</v>
       </c>
-      <c r="D29" s="5" t="s">
+    </row>
+    <row r="31" spans="1:6" ht="28.5">
+      <c r="A31" s="5" t="s">
         <v>527</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="B31" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>500</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="5" t="s">
+      <c r="E31" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="C30" s="5" t="s">
+      <c r="F31" s="5" t="s">
         <v>531</v>
       </c>
-      <c r="D30" s="5" t="s">
+    </row>
+    <row r="32" spans="1:6" ht="28.5">
+      <c r="A32" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="B32" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>533</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="D32" s="5" t="s">
         <v>534</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>500</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="27.6">
-      <c r="A31" s="5" t="s">
+      <c r="E32" s="5" t="s">
         <v>535</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="C31" s="5" t="s">
+      <c r="F32" s="5" t="s">
         <v>536</v>
       </c>
-      <c r="D31" s="5" t="s">
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="B33" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>538</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>539</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>500</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="27.6">
-      <c r="A32" s="5" t="s">
-        <v>540</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>543</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>544</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>500</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="5" t="s">
-        <v>545</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>546</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>548</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>549</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" s="5" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>553</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>549</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" s="5" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>161</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>557</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>558</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" s="5" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>563</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>500</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" s="5" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>102</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" s="5" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>202</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>571</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>558</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" s="5" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5" t="s">
         <v>70</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>574</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" s="5" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>579</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>549</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41" s="5" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>584</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>585</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="55.2">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="57">
       <c r="A42" s="5" t="s">
-        <v>586</v>
+        <v>575</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>587</v>
+        <v>576</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>590</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>500</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>443</v>
+        <v>579</v>
       </c>
     </row>
   </sheetData>
